--- a/registration_forms/022_preteen_activity_registration--registration_forms.xlsx
+++ b/registration_forms/022_preteen_activity_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
